--- a/data/trans_camb/IP09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 50,01</t>
+          <t>-17,17; 48,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 54,07</t>
+          <t>-31,51; 54,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 89,77</t>
+          <t>-12,89; 94,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 57,98</t>
+          <t>-9,0; 61,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 72,92</t>
+          <t>-34,08; 73,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 51,39</t>
+          <t>-18,53; 52,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 44,21</t>
+          <t>-3,75; 43,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 47,73</t>
+          <t>-22,03; 46,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 66,48</t>
+          <t>0,87; 67,23</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 716,19</t>
+          <t>-38,86; 707,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 443,76</t>
+          <t>-20,87; 411,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 411,63</t>
+          <t>-100,0; 486,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,78; 339,26</t>
+          <t>-40,68; 593,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 296,94</t>
+          <t>-9,8; 270,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 311,5</t>
+          <t>-63,79; 309,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 527,74</t>
+          <t>-7,94; 501,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 23,13</t>
+          <t>-8,97; 23,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 34,97</t>
+          <t>-2,02; 33,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 24,19</t>
+          <t>-13,13; 25,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 14,81</t>
+          <t>-11,25; 15,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 29,86</t>
+          <t>-6,08; 29,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 13,83</t>
+          <t>-19,83; 12,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 14,97</t>
+          <t>-5,36; 15,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 26,34</t>
+          <t>1,38; 27,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 13,64</t>
+          <t>-12,03; 13,32</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 138,1</t>
+          <t>-26,87; 157,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 219,53</t>
+          <t>-7,12; 199,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 144,75</t>
+          <t>-35,46; 132,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 65,37</t>
+          <t>-31,19; 72,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 132,49</t>
+          <t>-16,85; 127,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 58,63</t>
+          <t>-53,74; 51,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 64,08</t>
+          <t>-16,08; 67,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 113,82</t>
+          <t>4,03; 120,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 57,48</t>
+          <t>-35,72; 57,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 34,43</t>
+          <t>-12,75; 34,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 48,94</t>
+          <t>-3,77; 48,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 39,22</t>
+          <t>-8,61; 36,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 20,37</t>
+          <t>-21,2; 20,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 57,31</t>
+          <t>-2,99; 58,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 26,68</t>
+          <t>-22,32; 26,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 20,21</t>
+          <t>-11,87; 20,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 47,08</t>
+          <t>5,23; 43,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 24,93</t>
+          <t>-7,74; 26,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,8; 507,76</t>
+          <t>-59,72; 654,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 865,46</t>
+          <t>-27,13; 1074,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 725,08</t>
+          <t>-43,04; 805,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 172,06</t>
+          <t>-69,96; 188,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 457,46</t>
+          <t>-10,17; 458,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 232,54</t>
+          <t>-70,62; 207,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 184,65</t>
+          <t>-43,63; 159,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,47; 390,06</t>
+          <t>17,58; 352,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 217,25</t>
+          <t>-33,33; 229,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 24,55</t>
+          <t>-0,71; 23,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 30,69</t>
+          <t>3,92; 31,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 33,59</t>
+          <t>1,71; 36,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 15,9</t>
+          <t>-6,24; 15,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 30,91</t>
+          <t>4,58; 30,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 13,15</t>
+          <t>-12,25; 12,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 16,68</t>
+          <t>-1,39; 15,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 28,02</t>
+          <t>6,05; 26,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 18,29</t>
+          <t>-3,49; 17,74</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 162,37</t>
+          <t>-3,05; 147,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 191,37</t>
+          <t>10,14; 185,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 199,92</t>
+          <t>2,11; 214,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 67,06</t>
+          <t>-17,27; 68,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,96; 132,31</t>
+          <t>12,38; 127,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 55,18</t>
+          <t>-36,24; 52,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 79,17</t>
+          <t>-4,63; 70,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,02; 125,12</t>
+          <t>20,67; 120,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 83,37</t>
+          <t>-11,99; 76,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 48,69</t>
+          <t>-18,36; 48,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 54,64</t>
+          <t>-32,02; 54,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 94,79</t>
+          <t>-15,37; 88,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 61,02</t>
+          <t>-13,78; 56,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 73,14</t>
+          <t>-39,57; 67,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 52,83</t>
+          <t>-19,81; 50,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 43,63</t>
+          <t>-5,59; 43,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 46,05</t>
+          <t>-24,85; 44,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 67,23</t>
+          <t>-0,57; 62,51</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 707,9</t>
+          <t>-47,06; 660,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 411,86</t>
+          <t>-25,66; 385,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 486,6</t>
+          <t>-100,0; 347,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 593,48</t>
+          <t>-44,73; 310,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 270,49</t>
+          <t>-12,29; 305,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,79; 309,43</t>
+          <t>-68,27; 247,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 501,47</t>
+          <t>-5,54; 422,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 23,51</t>
+          <t>-9,77; 24,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 33,94</t>
+          <t>-2,4; 35,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 25,16</t>
+          <t>-12,11; 23,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 15,83</t>
+          <t>-9,87; 16,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 29,49</t>
+          <t>-1,96; 29,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 12,68</t>
+          <t>-18,5; 13,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 15,36</t>
+          <t>-6,68; 14,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 27,22</t>
+          <t>1,43; 27,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 13,32</t>
+          <t>-12,05; 12,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 157,43</t>
+          <t>-27,57; 147,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 199,26</t>
+          <t>-8,77; 204,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 132,11</t>
+          <t>-34,76; 141,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 72,57</t>
+          <t>-27,07; 77,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 127,85</t>
+          <t>-5,29; 126,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 51,73</t>
+          <t>-50,44; 53,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 67,12</t>
+          <t>-19,99; 62,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 120,98</t>
+          <t>4,4; 121,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 57,98</t>
+          <t>-37,65; 47,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 34,21</t>
+          <t>-13,01; 32,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 48,74</t>
+          <t>-5,45; 48,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 36,76</t>
+          <t>-8,28; 38,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 20,23</t>
+          <t>-23,19; 21,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 58,81</t>
+          <t>1,9; 60,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 26,64</t>
+          <t>-19,74; 27,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 20,53</t>
+          <t>-10,8; 19,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 43,72</t>
+          <t>6,1; 46,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 26,3</t>
+          <t>-9,02; 24,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 654,08</t>
+          <t>-65,08; 654,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 1074,27</t>
+          <t>-38,5; 962,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 805,87</t>
+          <t>-41,75; 817,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,96; 188,62</t>
+          <t>-70,55; 207,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 458,25</t>
+          <t>-5,93; 441,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 207,77</t>
+          <t>-60,35; 251,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,63; 159,71</t>
+          <t>-40,3; 164,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,58; 352,56</t>
+          <t>21,74; 404,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 229,04</t>
+          <t>-34,53; 208,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 23,39</t>
+          <t>-0,74; 23,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 31,46</t>
+          <t>3,13; 33,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 36,06</t>
+          <t>1,73; 37,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 15,23</t>
+          <t>-6,33; 16,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 30,36</t>
+          <t>3,73; 31,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 12,94</t>
+          <t>-11,9; 13,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 15,4</t>
+          <t>-0,83; 15,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,05; 26,69</t>
+          <t>8,1; 28,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 17,74</t>
+          <t>-3,14; 17,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 147,02</t>
+          <t>-4,51; 144,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,14; 185,73</t>
+          <t>8,77; 204,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 214,68</t>
+          <t>1,81; 222,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 68,12</t>
+          <t>-18,19; 71,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,38; 127,46</t>
+          <t>12,24; 137,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 52,1</t>
+          <t>-36,6; 56,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 70,76</t>
+          <t>-3,04; 70,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,67; 120,79</t>
+          <t>26,08; 133,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 76,84</t>
+          <t>-10,86; 77,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>17,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,97</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,23</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,67</t>
+          <t>12,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30,58</t>
+          <t>19,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 48,17</t>
+          <t>-10,2; 57,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 54,27</t>
+          <t>-36,91; 72,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 88,17</t>
+          <t>-17,43; 54,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 56,17</t>
+          <t>-15,4; 50,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 67,27</t>
+          <t>-33,5; 54,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 50,01</t>
+          <t>-31,19; 60,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 43,81</t>
+          <t>-4,23; 44,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 44,71</t>
+          <t>-21,45; 47,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 62,51</t>
+          <t>-11,13; 47,18</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>61,12%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>71,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>28,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>193,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>61,12%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104,02%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 660,74</t>
+          <t>-19,12; 443,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 411,63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-39,68; 365,97</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-40,23; 716,19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-25,66; 385,7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 347,38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-44,73; 310,41</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 305,92</t>
+          <t>-11,57; 296,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,27; 247,03</t>
+          <t>-62,86; 311,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 422,66</t>
+          <t>-26,24; 305,97</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,13</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>16,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,42</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>2,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 24,32</t>
+          <t>-12,24; 14,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 35,27</t>
+          <t>-4,23; 29,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 23,85</t>
+          <t>-16,84; 15,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 16,88</t>
+          <t>-9,62; 23,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 29,89</t>
+          <t>-3,55; 34,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 13,7</t>
+          <t>-11,72; 25,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 14,71</t>
+          <t>-7,09; 14,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 27,18</t>
+          <t>0,72; 26,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 12,12</t>
+          <t>-11,1; 15,04</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-3,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>62,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,66%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,82%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 147,61</t>
+          <t>-32,75; 65,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 204,88</t>
+          <t>-12,25; 132,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 141,11</t>
+          <t>-46,74; 63,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 77,29</t>
+          <t>-25,75; 138,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 126,25</t>
+          <t>-11,66; 219,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 53,99</t>
+          <t>-34,62; 152,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 62,9</t>
+          <t>-20,43; 64,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 121,46</t>
+          <t>2,86; 113,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 47,19</t>
+          <t>-32,73; 63,77</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31,52</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>22,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>31,52</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>14,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>8,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 32,96</t>
+          <t>-22,96; 20,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 48,3</t>
+          <t>1,09; 57,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 38,8</t>
+          <t>-20,01; 27,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 21,47</t>
+          <t>-15,78; 34,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 60,29</t>
+          <t>-5,54; 48,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 27,19</t>
+          <t>-9,5; 39,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 19,99</t>
+          <t>-10,84; 20,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 46,47</t>
+          <t>6,11; 47,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 24,27</t>
+          <t>-6,74; 25,56</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-6,62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>66,53%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>136,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-6,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>136,25%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 654,55</t>
+          <t>-68,19; 172,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 962,6</t>
+          <t>4,36; 457,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 817,74</t>
+          <t>-61,13; 239,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 207,81</t>
+          <t>-67,8; 507,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 441,76</t>
+          <t>-37,19; 865,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 251,4</t>
+          <t>-45,65; 712,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 164,75</t>
+          <t>-43,27; 184,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,74; 404,83</t>
+          <t>19,47; 390,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 208,58</t>
+          <t>-25,23; 214,55</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17,41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>11,51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>17,72</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15,31</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 23,05</t>
+          <t>-6,7; 15,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 33,18</t>
+          <t>2,46; 30,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 37,29</t>
+          <t>-11,24; 14,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 16,13</t>
+          <t>-0,73; 24,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 31,16</t>
+          <t>2,15; 30,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 13,14</t>
+          <t>-3,26; 23,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 15,45</t>
+          <t>-0,29; 16,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,1; 28,92</t>
+          <t>7,24; 28,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 17,86</t>
+          <t>-3,32; 15,17</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>50,56%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>77,88%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 144,58</t>
+          <t>-18,99; 67,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,77; 204,64</t>
+          <t>6,96; 132,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 222,99</t>
+          <t>-34,38; 59,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 71,91</t>
+          <t>-3,38; 162,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,24; 137,67</t>
+          <t>8,12; 191,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 56,23</t>
+          <t>-12,54; 153,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 70,84</t>
+          <t>-1,4; 79,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,08; 133,99</t>
+          <t>22,02; 125,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 77,03</t>
+          <t>-11,43; 67,79</t>
         </is>
       </c>
     </row>
